--- a/data/fertigation/input/system-interfaces.xlsx
+++ b/data/fertigation/input/system-interfaces.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R7948dd65172d499c"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备端口" sheetId="2" r:id="Rff54c74659504556"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="连接关系" sheetId="3" r:id="R2905de665d744c06"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测点" sheetId="4" r:id="R8d4289ef3ca046dd"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管材" sheetId="5" r:id="R9523f24d65474469"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="过滤参数" sheetId="6" r:id="R6bd24e839bae4798"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R79d57997230f4a2d"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备端口" sheetId="2" r:id="R99f45ecb19a54b2e"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="连接关系" sheetId="3" r:id="R89e0fda30e0b4b75"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测点" sheetId="4" r:id="Rd63c44ea63624ab9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管材" sheetId="5" r:id="Raca110da4ac34b7d"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="过滤参数" sheetId="6" r:id="Raf0a12bd90914255"/>
   </sheets>
 </workbook>
 </file>
@@ -176,7 +176,7 @@
         <color rgb="FF0A6B3A"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDDF3E7"/>
         </patternFill>
       </fill>
@@ -187,7 +187,7 @@
         <color rgb="FF8A4D00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFE7C2"/>
         </patternFill>
       </fill>
@@ -198,7 +198,7 @@
         <color rgb="FF7A5A00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF3C4"/>
         </patternFill>
       </fill>
@@ -209,7 +209,7 @@
         <color rgb="FF9D2222"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFADDDD"/>
         </patternFill>
       </fill>
@@ -220,7 +220,7 @@
         <color rgb="FF0A6B3A"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDDF3E7"/>
         </patternFill>
       </fill>
@@ -231,7 +231,7 @@
         <color rgb="FF8A4D00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFE7C2"/>
         </patternFill>
       </fill>
@@ -242,7 +242,7 @@
         <color rgb="FF7A5A00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF3C4"/>
         </patternFill>
       </fill>
@@ -253,7 +253,7 @@
         <color rgb="FF9D2222"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFADDDD"/>
         </patternFill>
       </fill>
@@ -264,7 +264,7 @@
         <color rgb="FF0A6B3A"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDDF3E7"/>
         </patternFill>
       </fill>
@@ -275,7 +275,7 @@
         <color rgb="FF8A4D00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFE7C2"/>
         </patternFill>
       </fill>
@@ -286,7 +286,7 @@
         <color rgb="FF7A5A00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF3C4"/>
         </patternFill>
       </fill>
@@ -297,7 +297,7 @@
         <color rgb="FF9D2222"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFADDDD"/>
         </patternFill>
       </fill>
@@ -308,7 +308,7 @@
         <color rgb="FF0A6B3A"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDDF3E7"/>
         </patternFill>
       </fill>
@@ -319,7 +319,7 @@
         <color rgb="FF8A4D00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFE7C2"/>
         </patternFill>
       </fill>
@@ -330,7 +330,7 @@
         <color rgb="FF7A5A00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF3C4"/>
         </patternFill>
       </fill>
@@ -341,7 +341,7 @@
         <color rgb="FF9D2222"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFADDDD"/>
         </patternFill>
       </fill>
@@ -352,7 +352,7 @@
         <color rgb="FF0A6B3A"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFDDF3E7"/>
         </patternFill>
       </fill>
@@ -363,7 +363,7 @@
         <color rgb="FF8A4D00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFE7C2"/>
         </patternFill>
       </fill>
@@ -374,7 +374,7 @@
         <color rgb="FF7A5A00"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF3C4"/>
         </patternFill>
       </fill>
@@ -385,7 +385,7 @@
         <color rgb="FF9D2222"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFADDDD"/>
         </patternFill>
       </fill>
@@ -601,7 +601,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="str">
-        <v>双路水肥系统 · 接口规格事实簿</v>
+        <v>双液源双末端水肥药系统 · 接口规格事实簿</v>
       </c>
       <c r="B1" s="4" t="str">
         <v>双路水肥系统 · 接口规格事实簿</v>
@@ -627,7 +627,7 @@
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="8" t="str">
-        <v>本工作簿是设备接口、牙型、管径、过滤参数与测点的人工维护入口；黄色字段允许修改，生成后的JSON不得手工修改。</v>
+        <v>本工作簿是双液源、共用文丘里、滴灌/上空喷灌接口事实的人工维护入口；黄色字段允许修改，生成后的JSON不得手工修改。</v>
       </c>
       <c r="B2" s="8" t="str">
         <v>本工作簿是设备接口、牙型、管径、过滤参数与测点的人工维护入口；黄色字段允许修改，生成后的JSON不得手工修改。</v>
@@ -667,7 +667,7 @@
         <v>design_revision</v>
       </c>
       <c r="B5" s="22" t="str">
-        <v>2026-07-24-v3</v>
+        <v>2026-07-24-v4</v>
       </c>
       <c r="C5" s="20" t="str">
         <v>设计事实版本；变更接口或管径时递增</v>
@@ -700,7 +700,7 @@
         <v>source_note</v>
       </c>
       <c r="B8" s="23" t="str">
-        <v>当前均为候选设计，具体商品型号尚未确认</v>
+        <v>V4为双液源双末端候选设计；当前使用两只带中位全关的三通手动选择阀，具体阀门、喷头、管径和材料仍待厂家确认</v>
       </c>
       <c r="C8" s="21" t="str">
         <v>不得把候选尺寸写成采购通过</v>
@@ -814,7 +814,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="str">
-        <v>设备端口与牙型</v>
+        <v>双液源、滴灌/喷灌设备端口与牙型</v>
       </c>
       <c r="B1" s="4" t="str">
         <v>设备端口与牙型</v>
@@ -923,6 +923,26 @@
       <c r="R2" s="8" t="str">
         <v>G1/2（4分）和G1/4（2分）均为候选。状态改为“已确定”前，必须补齐牙型、内外牙、密封方式和厂家资料。</v>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="14" t="str">
@@ -1352,14 +1372,14 @@
       <c r="M13" s="23"/>
       <c r="N13" s="23"/>
       <c r="O13" s="21" t="str">
-        <v>耐清水材料待确认</v>
+        <v>POM/PP/EPDM等耐清水工程塑料待确认</v>
       </c>
       <c r="P13" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="Q13" s="23"/>
       <c r="R13" s="23" t="str">
-        <v>箭头指向合流点；需低开启压力</v>
+        <v>优先工程塑料低开启压力止回阀；箭头指向A/B合流点</v>
       </c>
     </row>
     <row r="14">
@@ -1398,14 +1418,14 @@
       <c r="M14" s="23"/>
       <c r="N14" s="23"/>
       <c r="O14" s="21" t="str">
-        <v>耐清水材料待确认</v>
+        <v>POM/PP/EPDM等耐清水工程塑料待确认</v>
       </c>
       <c r="P14" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="Q14" s="23"/>
       <c r="R14" s="23" t="str">
-        <v>箭头指向合流点</v>
+        <v>优先工程塑料低开启压力止回阀；箭头指向A/B合流点</v>
       </c>
     </row>
     <row r="15">
@@ -1500,7 +1520,7 @@
         <v>VENTURI</v>
       </c>
       <c r="C17" s="21" t="str">
-        <v>文丘里</v>
+        <v>共用文丘里</v>
       </c>
       <c r="D17" s="21" t="str">
         <v>侧吸口</v>
@@ -1524,7 +1544,7 @@
       <c r="M17" s="23"/>
       <c r="N17" s="23"/>
       <c r="O17" s="21" t="str">
-        <v>耐肥材料待确认</v>
+        <v>耐肥液/农药材料待确认</v>
       </c>
       <c r="P17" s="23" t="str">
         <v>待厂家确认</v>
@@ -1570,14 +1590,14 @@
       <c r="M18" s="23"/>
       <c r="N18" s="23"/>
       <c r="O18" s="21" t="str">
-        <v>耐肥液材料待确认</v>
+        <v>POM/PP/PVDF/EPDM等耐肥液/农药工程塑料待确认</v>
       </c>
       <c r="P18" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="Q18" s="23"/>
       <c r="R18" s="23" t="str">
-        <v>安装在文丘里出口后</v>
+        <v>优先工程塑料低开启压力止回阀；安装在文丘里出口后并指向A/B合流点</v>
       </c>
     </row>
     <row r="19">
@@ -1616,14 +1636,14 @@
       <c r="M19" s="23"/>
       <c r="N19" s="23"/>
       <c r="O19" s="21" t="str">
-        <v>耐肥液材料待确认</v>
+        <v>POM/PP/PVDF/EPDM等耐肥液/农药工程塑料待确认</v>
       </c>
       <c r="P19" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="Q19" s="23"/>
       <c r="R19" s="23" t="str">
-        <v>箭头指向合流点</v>
+        <v>优先工程塑料低开启压力止回阀；安装在文丘里出口后并指向A/B合流点</v>
       </c>
     </row>
     <row r="20">
@@ -1757,10 +1777,10 @@
         <v>REG-IN</v>
       </c>
       <c r="B23" s="21" t="str">
-        <v>REG</v>
+        <v>REG-D</v>
       </c>
       <c r="C23" s="21" t="str">
-        <v>减压阀</v>
+        <v>滴灌减压阀</v>
       </c>
       <c r="D23" s="21" t="str">
         <v>入口</v>
@@ -1787,22 +1807,26 @@
       <c r="L23" s="23"/>
       <c r="M23" s="23"/>
       <c r="N23" s="23"/>
-      <c r="O23" s="21"/>
+      <c r="O23" s="21" t="str">
+        <v>PP/POM/EPDM等耐肥液工程塑料待确认</v>
+      </c>
       <c r="P23" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
+      <c r="R23" s="23" t="str">
+        <v>滴灌塑料减压/调压件，不是止回阀；9/12滴灌支路不另加止回阀</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="21" t="str">
         <v>REG-OUT</v>
       </c>
       <c r="B24" s="21" t="str">
-        <v>REG</v>
+        <v>REG-D</v>
       </c>
       <c r="C24" s="21" t="str">
-        <v>减压阀</v>
+        <v>滴灌减压阀</v>
       </c>
       <c r="D24" s="21" t="str">
         <v>出口</v>
@@ -1829,12 +1853,16 @@
       <c r="L24" s="23"/>
       <c r="M24" s="23"/>
       <c r="N24" s="23"/>
-      <c r="O24" s="21"/>
+      <c r="O24" s="21" t="str">
+        <v>PP/POM/EPDM等耐肥液工程塑料待确认</v>
+      </c>
       <c r="P24" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
+      <c r="R24" s="23" t="str">
+        <v>滴灌塑料减压/调压件，不是止回阀；9/12滴灌支路不另加止回阀</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="21" t="str">
@@ -1844,7 +1872,7 @@
         <v>PIPE-MAIN</v>
       </c>
       <c r="C25" s="21" t="str">
-        <v>9/12 PE主管</v>
+        <v>9/12滴灌主管</v>
       </c>
       <c r="D25" s="21" t="str">
         <v>入口</v>
@@ -1888,7 +1916,7 @@
         <v>PIPE-MAIN</v>
       </c>
       <c r="C26" s="21" t="str">
-        <v>9/12 PE主管</v>
+        <v>9/12滴灌主管</v>
       </c>
       <c r="D26" s="21" t="str">
         <v>末端/分配口</v>
@@ -2062,7 +2090,7 @@
         <v>BUCKET-FILTER</v>
       </c>
       <c r="C30" s="21" t="str">
-        <v>桶内过滤头</v>
+        <v>肥料桶过滤头</v>
       </c>
       <c r="D30" s="21" t="str">
         <v>出口</v>
@@ -2086,7 +2114,7 @@
       <c r="M30" s="23"/>
       <c r="N30" s="23"/>
       <c r="O30" s="21" t="str">
-        <v>耐肥材料待确认</v>
+        <v>耐肥液材料待确认</v>
       </c>
       <c r="P30" s="23" t="str">
         <v>待厂家确认</v>
@@ -2099,10 +2127,10 @@
         <v>ADJ-IN</v>
       </c>
       <c r="B31" s="21" t="str">
-        <v>ADJ</v>
+        <v>ADJ-F</v>
       </c>
       <c r="C31" s="21" t="str">
-        <v>吸肥调节阀</v>
+        <v>肥料吸液调节阀</v>
       </c>
       <c r="D31" s="21" t="str">
         <v>入口</v>
@@ -2126,7 +2154,7 @@
       <c r="M31" s="23"/>
       <c r="N31" s="23"/>
       <c r="O31" s="21" t="str">
-        <v>耐肥材料待确认</v>
+        <v>耐肥液材料待确认</v>
       </c>
       <c r="P31" s="23" t="str">
         <v>待厂家确认</v>
@@ -2139,10 +2167,10 @@
         <v>ADJ-OUT</v>
       </c>
       <c r="B32" s="21" t="str">
-        <v>ADJ</v>
+        <v>ADJ-F</v>
       </c>
       <c r="C32" s="21" t="str">
-        <v>吸肥调节阀</v>
+        <v>肥料吸液调节阀</v>
       </c>
       <c r="D32" s="21" t="str">
         <v>出口</v>
@@ -2166,7 +2194,7 @@
       <c r="M32" s="23"/>
       <c r="N32" s="23"/>
       <c r="O32" s="21" t="str">
-        <v>耐肥材料待确认</v>
+        <v>耐肥液材料待确认</v>
       </c>
       <c r="P32" s="23" t="str">
         <v>待厂家确认</v>
@@ -2179,10 +2207,10 @@
         <v>CV-S-IN</v>
       </c>
       <c r="B33" s="21" t="str">
-        <v>CV-S</v>
+        <v>CV-F</v>
       </c>
       <c r="C33" s="21" t="str">
-        <v>吸肥止回阀</v>
+        <v>肥料吸液止回阀</v>
       </c>
       <c r="D33" s="21" t="str">
         <v>入口</v>
@@ -2206,14 +2234,14 @@
       <c r="M33" s="23"/>
       <c r="N33" s="23"/>
       <c r="O33" s="21" t="str">
-        <v>PP/PVDF/EPDM待确认</v>
+        <v>PP/PVDF/EPDM/FKM等耐对应母液工程塑料待确认</v>
       </c>
       <c r="P33" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="Q33" s="23"/>
       <c r="R33" s="23" t="str">
-        <v>箭头指向文丘里；需低开启压力</v>
+        <v>工程塑料低开启压力止回阀；箭头指向MV-SOURCE和文丘里</v>
       </c>
     </row>
     <row r="34">
@@ -2221,10 +2249,10 @@
         <v>CV-S-OUT</v>
       </c>
       <c r="B34" s="21" t="str">
-        <v>CV-S</v>
+        <v>CV-F</v>
       </c>
       <c r="C34" s="21" t="str">
-        <v>吸肥止回阀</v>
+        <v>肥料吸液止回阀</v>
       </c>
       <c r="D34" s="21" t="str">
         <v>出口</v>
@@ -2248,15 +2276,953 @@
       <c r="M34" s="23"/>
       <c r="N34" s="23"/>
       <c r="O34" s="21" t="str">
-        <v>PP/PVDF/EPDM待确认</v>
+        <v>PP/PVDF/EPDM/FKM等耐对应母液工程塑料待确认</v>
       </c>
       <c r="P34" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="Q34" s="23"/>
       <c r="R34" s="23" t="str">
-        <v>箭头指向文丘里</v>
-      </c>
+        <v>工程塑料低开启压力止回阀；箭头指向MV-SOURCE和文丘里</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>MV-END-COM</v>
+      </c>
+      <c r="B35" t="str">
+        <v>MV-END</v>
+      </c>
+      <c r="C35" t="str">
+        <v>滴灌/喷灌三通选择阀</v>
+      </c>
+      <c r="D35" t="str">
+        <v>公共入口</v>
+      </c>
+      <c r="E35" t="str">
+        <v>G</v>
+      </c>
+      <c r="F35" t="str">
+        <v>1/2</v>
+      </c>
+      <c r="G35" t="str">
+        <v>俗称4分</v>
+      </c>
+      <c r="H35" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="I35" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="J35" t="str">
+        <v>螺纹</v>
+      </c>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35" t="str">
+        <v>耐肥液/农药材料待确认</v>
+      </c>
+      <c r="P35" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q35"/>
+      <c r="R35" t="str">
+        <v>三位三通选择阀；须有滴灌/中位全关/喷灌三个锁定位置，禁止内部串通</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>MV-END-D</v>
+      </c>
+      <c r="B36" t="str">
+        <v>MV-END</v>
+      </c>
+      <c r="C36" t="str">
+        <v>滴灌/喷灌三通选择阀</v>
+      </c>
+      <c r="D36" t="str">
+        <v>滴灌出口</v>
+      </c>
+      <c r="E36" t="str">
+        <v>G</v>
+      </c>
+      <c r="F36" t="str">
+        <v>1/2</v>
+      </c>
+      <c r="G36" t="str">
+        <v>俗称4分</v>
+      </c>
+      <c r="H36" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="I36" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="J36" t="str">
+        <v>螺纹</v>
+      </c>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36" t="str">
+        <v>耐肥液/农药材料待确认</v>
+      </c>
+      <c r="P36" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q36"/>
+      <c r="R36" t="str">
+        <v>仅在滴灌位与公共入口连通；滴灌设计流量压损待确认</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>MV-END-S</v>
+      </c>
+      <c r="B37" t="str">
+        <v>MV-END</v>
+      </c>
+      <c r="C37" t="str">
+        <v>滴灌/喷灌三通选择阀</v>
+      </c>
+      <c r="D37" t="str">
+        <v>喷灌出口</v>
+      </c>
+      <c r="E37" t="str">
+        <v>G</v>
+      </c>
+      <c r="F37" t="str">
+        <v>1/2</v>
+      </c>
+      <c r="G37" t="str">
+        <v>俗称4分</v>
+      </c>
+      <c r="H37" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="I37" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="J37" t="str">
+        <v>螺纹</v>
+      </c>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37" t="str">
+        <v>耐肥液/农药材料待确认</v>
+      </c>
+      <c r="P37" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q37"/>
+      <c r="R37" t="str">
+        <v>仅在喷灌位与公共入口连通；喷灌设计流量压损待确认</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>FILTER-S-IN</v>
+      </c>
+      <c r="B38" t="str">
+        <v>FILTER-S</v>
+      </c>
+      <c r="C38" t="str">
+        <v>喷灌支路过滤器</v>
+      </c>
+      <c r="D38" t="str">
+        <v>入口</v>
+      </c>
+      <c r="E38" t="str">
+        <v>G</v>
+      </c>
+      <c r="F38" t="str">
+        <v>1/2</v>
+      </c>
+      <c r="G38" t="str">
+        <v>俗称4分</v>
+      </c>
+      <c r="H38" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="I38" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="J38" t="str">
+        <v>螺纹</v>
+      </c>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38" t="str">
+        <v>耐农药材料待确认</v>
+      </c>
+      <c r="P38" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q38"/>
+      <c r="R38" t="str">
+        <v>过滤精度按喷头厂家要求</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>FILTER-S-OUT</v>
+      </c>
+      <c r="B39" t="str">
+        <v>FILTER-S</v>
+      </c>
+      <c r="C39" t="str">
+        <v>喷灌支路过滤器</v>
+      </c>
+      <c r="D39" t="str">
+        <v>出口</v>
+      </c>
+      <c r="E39" t="str">
+        <v>G</v>
+      </c>
+      <c r="F39" t="str">
+        <v>1/2</v>
+      </c>
+      <c r="G39" t="str">
+        <v>俗称4分</v>
+      </c>
+      <c r="H39" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="I39" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="J39" t="str">
+        <v>螺纹</v>
+      </c>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39" t="str">
+        <v>耐农药材料待确认</v>
+      </c>
+      <c r="P39" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q39"/>
+      <c r="R39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>REG-S-IN</v>
+      </c>
+      <c r="B40" t="str">
+        <v>REG-S</v>
+      </c>
+      <c r="C40" t="str">
+        <v>喷灌调压阀</v>
+      </c>
+      <c r="D40" t="str">
+        <v>入口</v>
+      </c>
+      <c r="E40" t="str">
+        <v>G</v>
+      </c>
+      <c r="F40" t="str">
+        <v>1/2</v>
+      </c>
+      <c r="G40" t="str">
+        <v>俗称4分</v>
+      </c>
+      <c r="H40" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="I40" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="J40" t="str">
+        <v>螺纹</v>
+      </c>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40" t="str">
+        <v>耐农药材料待确认</v>
+      </c>
+      <c r="P40" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q40"/>
+      <c r="R40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>REG-S-OUT</v>
+      </c>
+      <c r="B41" t="str">
+        <v>REG-S</v>
+      </c>
+      <c r="C41" t="str">
+        <v>喷灌调压阀</v>
+      </c>
+      <c r="D41" t="str">
+        <v>出口</v>
+      </c>
+      <c r="E41" t="str">
+        <v>G</v>
+      </c>
+      <c r="F41" t="str">
+        <v>1/2</v>
+      </c>
+      <c r="G41" t="str">
+        <v>俗称4分</v>
+      </c>
+      <c r="H41" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="I41" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="J41" t="str">
+        <v>螺纹</v>
+      </c>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41" t="str">
+        <v>耐农药材料待确认</v>
+      </c>
+      <c r="P41" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q41"/>
+      <c r="R41" t="str">
+        <v>P5按最不利喷头位置实测</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>SPRAY-MAIN-IN</v>
+      </c>
+      <c r="B42" t="str">
+        <v>PIPE-SPRAY</v>
+      </c>
+      <c r="C42" t="str">
+        <v>喷灌主管</v>
+      </c>
+      <c r="D42" t="str">
+        <v>入口</v>
+      </c>
+      <c r="E42" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42" t="str">
+        <v>软管</v>
+      </c>
+      <c r="I42" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J42" t="str">
+        <v>PE管接头/卡箍</v>
+      </c>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42" t="str">
+        <v>PE/耐农药材料待确认</v>
+      </c>
+      <c r="P42" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q42"/>
+      <c r="R42" t="str">
+        <v>内外径按喷头总流量重新计算</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>SPRAY-MAIN-OUT</v>
+      </c>
+      <c r="B43" t="str">
+        <v>PIPE-SPRAY</v>
+      </c>
+      <c r="C43" t="str">
+        <v>喷灌主管</v>
+      </c>
+      <c r="D43" t="str">
+        <v>末端/喷头接口</v>
+      </c>
+      <c r="E43" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43" t="str">
+        <v>软管</v>
+      </c>
+      <c r="I43" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J43" t="str">
+        <v>PE管接头/卡箍</v>
+      </c>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43" t="str">
+        <v>PE/耐农药材料待确认</v>
+      </c>
+      <c r="P43" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q43"/>
+      <c r="R43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>SPRINKLER-IN</v>
+      </c>
+      <c r="B44" t="str">
+        <v>SPRINKLER</v>
+      </c>
+      <c r="C44" t="str">
+        <v>上空喷头</v>
+      </c>
+      <c r="D44" t="str">
+        <v>入口</v>
+      </c>
+      <c r="E44" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44" t="str">
+        <v>倒钩</v>
+      </c>
+      <c r="I44" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J44" t="str">
+        <v>喷头接头待确认</v>
+      </c>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44" t="str">
+        <v>耐农药材料待确认</v>
+      </c>
+      <c r="P44" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q44"/>
+      <c r="R44" t="str">
+        <v>流量、压力、覆盖半径和防滴漏能力待确认</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>PEST-FILTER-OUT</v>
+      </c>
+      <c r="B45" t="str">
+        <v>PEST-FILTER</v>
+      </c>
+      <c r="C45" t="str">
+        <v>农药桶过滤头</v>
+      </c>
+      <c r="D45" t="str">
+        <v>出口</v>
+      </c>
+      <c r="E45" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45" t="str">
+        <v>倒钩</v>
+      </c>
+      <c r="I45" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J45" t="str">
+        <v>软管倒钩</v>
+      </c>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45" t="str">
+        <v>耐具体农药制剂材料待确认</v>
+      </c>
+      <c r="P45" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>https://zzys.moa.gov.cn/zcjd/201705/t20170506_5597923.htm</v>
+      </c>
+      <c r="R45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>ADJ-P-IN</v>
+      </c>
+      <c r="B46" t="str">
+        <v>ADJ-P</v>
+      </c>
+      <c r="C46" t="str">
+        <v>农药吸液调节阀</v>
+      </c>
+      <c r="D46" t="str">
+        <v>入口</v>
+      </c>
+      <c r="E46" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46" t="str">
+        <v>倒钩</v>
+      </c>
+      <c r="I46" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J46" t="str">
+        <v>软管倒钩</v>
+      </c>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46" t="str">
+        <v>耐具体农药制剂材料待确认</v>
+      </c>
+      <c r="P46" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>https://zzys.moa.gov.cn/zcjd/201705/t20170506_5597923.htm</v>
+      </c>
+      <c r="R46"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>ADJ-P-OUT</v>
+      </c>
+      <c r="B47" t="str">
+        <v>ADJ-P</v>
+      </c>
+      <c r="C47" t="str">
+        <v>农药吸液调节阀</v>
+      </c>
+      <c r="D47" t="str">
+        <v>出口</v>
+      </c>
+      <c r="E47" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47" t="str">
+        <v>倒钩</v>
+      </c>
+      <c r="I47" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J47" t="str">
+        <v>软管倒钩</v>
+      </c>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47" t="str">
+        <v>耐具体农药制剂材料待确认</v>
+      </c>
+      <c r="P47" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q47" t="str">
+        <v>https://zzys.moa.gov.cn/zcjd/201705/t20170506_5597923.htm</v>
+      </c>
+      <c r="R47"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>CV-P-IN</v>
+      </c>
+      <c r="B48" t="str">
+        <v>CV-P</v>
+      </c>
+      <c r="C48" t="str">
+        <v>农药吸液止回阀</v>
+      </c>
+      <c r="D48" t="str">
+        <v>入口</v>
+      </c>
+      <c r="E48" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48" t="str">
+        <v>倒钩</v>
+      </c>
+      <c r="I48" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J48" t="str">
+        <v>软管倒钩</v>
+      </c>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48" t="str">
+        <v>PP/PVDF/EPDM/FKM等耐对应母液工程塑料待确认</v>
+      </c>
+      <c r="P48" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q48"/>
+      <c r="R48" t="str">
+        <v>工程塑料低开启压力止回阀；箭头指向MV-SOURCE和文丘里</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>CV-P-OUT</v>
+      </c>
+      <c r="B49" t="str">
+        <v>CV-P</v>
+      </c>
+      <c r="C49" t="str">
+        <v>农药吸液止回阀</v>
+      </c>
+      <c r="D49" t="str">
+        <v>出口</v>
+      </c>
+      <c r="E49" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49" t="str">
+        <v>倒钩</v>
+      </c>
+      <c r="I49" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J49" t="str">
+        <v>软管倒钩</v>
+      </c>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="O49" t="str">
+        <v>PP/PVDF/EPDM/FKM等耐对应母液工程塑料待确认</v>
+      </c>
+      <c r="P49" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q49"/>
+      <c r="R49" t="str">
+        <v>工程塑料低开启压力止回阀；箭头指向MV-SOURCE和文丘里</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>MV-SOURCE-F</v>
+      </c>
+      <c r="B50" t="str">
+        <v>MV-SOURCE</v>
+      </c>
+      <c r="C50" t="str">
+        <v>肥料/农药三通选择阀</v>
+      </c>
+      <c r="D50" t="str">
+        <v>肥料入口</v>
+      </c>
+      <c r="E50" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50" t="str">
+        <v>倒钩</v>
+      </c>
+      <c r="I50" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J50" t="str">
+        <v>软管倒钩</v>
+      </c>
+      <c r="K50"/>
+      <c r="L50"/>
+      <c r="M50"/>
+      <c r="N50"/>
+      <c r="O50" t="str">
+        <v>耐肥液/农药及真空吸液材料待确认</v>
+      </c>
+      <c r="P50" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q50"/>
+      <c r="R50" t="str">
+        <v>仅在肥料位与公共出口连通</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>MV-SOURCE-P</v>
+      </c>
+      <c r="B51" t="str">
+        <v>MV-SOURCE</v>
+      </c>
+      <c r="C51" t="str">
+        <v>肥料/农药三通选择阀</v>
+      </c>
+      <c r="D51" t="str">
+        <v>农药入口</v>
+      </c>
+      <c r="E51" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51" t="str">
+        <v>倒钩</v>
+      </c>
+      <c r="I51" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J51" t="str">
+        <v>软管倒钩</v>
+      </c>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51"/>
+      <c r="O51" t="str">
+        <v>耐肥液/农药及真空吸液材料待确认</v>
+      </c>
+      <c r="P51" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q51"/>
+      <c r="R51" t="str">
+        <v>仅在农药位与公共出口连通</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>MV-SOURCE-COM</v>
+      </c>
+      <c r="B52" t="str">
+        <v>MV-SOURCE</v>
+      </c>
+      <c r="C52" t="str">
+        <v>肥料/农药三通选择阀</v>
+      </c>
+      <c r="D52" t="str">
+        <v>公共出口</v>
+      </c>
+      <c r="E52" t="str">
+        <v>无螺纹</v>
+      </c>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52" t="str">
+        <v>倒钩</v>
+      </c>
+      <c r="I52" t="str">
+        <v>卡箍/压紧</v>
+      </c>
+      <c r="J52" t="str">
+        <v>软管倒钩</v>
+      </c>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52"/>
+      <c r="O52" t="str">
+        <v>耐肥液/农药及真空吸液材料待确认</v>
+      </c>
+      <c r="P52" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="Q52"/>
+      <c r="R52" t="str">
+        <v>须有肥料/中位全关/农药三个锁定位置；需确认真空密封与无内部串通</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53"/>
+      <c r="O53"/>
+      <c r="P53"/>
+      <c r="Q53"/>
+      <c r="R53"/>
+    </row>
+    <row r="54">
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="M54"/>
+      <c r="N54"/>
+      <c r="O54"/>
+      <c r="P54"/>
+      <c r="Q54"/>
+      <c r="R54"/>
+    </row>
+    <row r="55">
+      <c r="A55"/>
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+      <c r="P55"/>
+      <c r="Q55"/>
+      <c r="R55"/>
+    </row>
+    <row r="56">
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
+      <c r="P56"/>
+      <c r="Q56"/>
+      <c r="R56"/>
+    </row>
+    <row r="57">
+      <c r="A57"/>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="O57"/>
+      <c r="P57"/>
+      <c r="Q57"/>
+      <c r="R57"/>
+    </row>
+    <row r="58">
+      <c r="A58"/>
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
+      <c r="L58"/>
+      <c r="M58"/>
+      <c r="N58"/>
+      <c r="O58"/>
+      <c r="P58"/>
+      <c r="Q58"/>
+      <c r="R58"/>
+    </row>
+    <row r="59">
+      <c r="A59"/>
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="M59"/>
+      <c r="N59"/>
+      <c r="O59"/>
+      <c r="P59"/>
+      <c r="Q59"/>
+      <c r="R59"/>
+    </row>
+    <row r="60">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+      <c r="K60"/>
+      <c r="L60"/>
+      <c r="M60"/>
+      <c r="N60"/>
+      <c r="O60"/>
+      <c r="P60"/>
+      <c r="Q60"/>
+      <c r="R60"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -2294,7 +3260,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="str">
-        <v>端口连接关系</v>
+        <v>双液源、滴灌/喷灌端口连接关系</v>
       </c>
       <c r="B1" s="4" t="str">
         <v>端口连接关系</v>
@@ -2344,6 +3310,16 @@
         <v>转接件由生成器根据已确认的牙型、尺寸、内外牙和密封面保守推导；任何待确认端口均不生成采购数量。</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="14" t="str">
         <v>连接ID</v>
@@ -2560,20 +3536,20 @@
         <v>MERGE-OUT</v>
       </c>
       <c r="C13" s="21" t="str">
-        <v>REG-IN</v>
+        <v>MV-END-COM</v>
       </c>
       <c r="D13" s="21" t="str">
-        <v>下游</v>
+        <v>共用下游</v>
       </c>
       <c r="E13" s="21" t="str">
-        <v>合流→主管</v>
+        <v>合流→末端分配</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="H13" s="23" t="str">
-        <v>先合流后减压</v>
+        <v>P3位于此段；末端由一只三通选择阀切换</v>
       </c>
     </row>
     <row r="14">
@@ -2581,23 +3557,23 @@
         <v>C10</v>
       </c>
       <c r="B14" s="21" t="str">
-        <v>REG-OUT</v>
+        <v>MV-END-D</v>
       </c>
       <c r="C14" s="21" t="str">
-        <v>MAIN-IN</v>
+        <v>REG-IN</v>
       </c>
       <c r="D14" s="21" t="str">
-        <v>下游</v>
+        <v>滴灌</v>
       </c>
       <c r="E14" s="21" t="str">
-        <v>合流→主管</v>
+        <v>分配→滴灌</v>
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="H14" s="23" t="str">
-        <v>P3位于减压阀后</v>
+        <v>MV-END处于滴灌位</v>
       </c>
     </row>
     <row r="15">
@@ -2605,23 +3581,23 @@
         <v>C11</v>
       </c>
       <c r="B15" s="21" t="str">
-        <v>MAIN-OUT</v>
+        <v>REG-OUT</v>
       </c>
       <c r="C15" s="21" t="str">
-        <v>LATERAL-IN</v>
+        <v>MAIN-IN</v>
       </c>
       <c r="D15" s="21" t="str">
-        <v>下游</v>
+        <v>滴灌</v>
       </c>
       <c r="E15" s="21" t="str">
-        <v>主管→支管</v>
+        <v>滴灌减压→主管</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23" t="str">
         <v>待厂家确认</v>
       </c>
       <c r="H15" s="23" t="str">
-        <v>N条代表性支管</v>
+        <v>P4位于滴灌减压阀后</v>
       </c>
     </row>
     <row r="16">
@@ -2629,38 +3605,40 @@
         <v>C12</v>
       </c>
       <c r="B16" s="21" t="str">
-        <v>LATERAL-OUT</v>
+        <v>MAIN-OUT</v>
       </c>
       <c r="C16" s="21" t="str">
-        <v>EMITTER-IN</v>
+        <v>LATERAL-IN</v>
       </c>
       <c r="D16" s="21" t="str">
-        <v>下游</v>
+        <v>滴灌</v>
       </c>
       <c r="E16" s="21" t="str">
-        <v>支管→滴头</v>
+        <v>主管→支管</v>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="23" t="str">
         <v>待厂家确认</v>
       </c>
-      <c r="H16" s="23"/>
+      <c r="H16" s="23" t="str">
+        <v>N条代表性支管</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="str">
         <v>C13</v>
       </c>
       <c r="B17" s="21" t="str">
-        <v>BUCKET-FILTER-OUT</v>
+        <v>LATERAL-OUT</v>
       </c>
       <c r="C17" s="21" t="str">
-        <v>ADJ-IN</v>
+        <v>EMITTER-IN</v>
       </c>
       <c r="D17" s="21" t="str">
-        <v>吸肥</v>
+        <v>滴灌</v>
       </c>
       <c r="E17" s="21" t="str">
-        <v>肥液桶→文丘里</v>
+        <v>支管→滴头</v>
       </c>
       <c r="F17" s="23"/>
       <c r="G17" s="23" t="str">
@@ -2673,46 +3651,292 @@
         <v>C14</v>
       </c>
       <c r="B18" s="21" t="str">
-        <v>ADJ-OUT</v>
+        <v>MV-END-S</v>
       </c>
       <c r="C18" s="21" t="str">
-        <v>CV-S-IN</v>
+        <v>FILTER-S-IN</v>
       </c>
       <c r="D18" s="21" t="str">
-        <v>吸肥</v>
+        <v>喷灌</v>
       </c>
       <c r="E18" s="21" t="str">
-        <v>肥液桶→文丘里</v>
+        <v>分配→喷灌</v>
       </c>
       <c r="F18" s="23"/>
       <c r="G18" s="23" t="str">
         <v>待厂家确认</v>
       </c>
-      <c r="H18" s="23"/>
+      <c r="H18" s="23" t="str">
+        <v>MV-END处于喷灌位</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="str">
         <v>C15</v>
       </c>
       <c r="B19" s="21" t="str">
-        <v>CV-S-OUT</v>
+        <v>FILTER-S-OUT</v>
       </c>
       <c r="C19" s="21" t="str">
-        <v>VENTURI-SUCTION</v>
+        <v>REG-S-IN</v>
       </c>
       <c r="D19" s="21" t="str">
-        <v>吸肥</v>
+        <v>喷灌</v>
       </c>
       <c r="E19" s="21" t="str">
-        <v>肥液桶→文丘里</v>
+        <v>过滤→调压</v>
       </c>
       <c r="F19" s="23"/>
       <c r="G19" s="23" t="str">
         <v>待厂家确认</v>
       </c>
-      <c r="H19" s="23" t="str">
-        <v>止回箭头指向文丘里</v>
-      </c>
+      <c r="H19" s="23"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>C16</v>
+      </c>
+      <c r="B20" t="str">
+        <v>REG-S-OUT</v>
+      </c>
+      <c r="C20" t="str">
+        <v>SPRAY-MAIN-IN</v>
+      </c>
+      <c r="D20" t="str">
+        <v>喷灌</v>
+      </c>
+      <c r="E20" t="str">
+        <v>调压→喷灌主管</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="H20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>C17</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SPRAY-MAIN-OUT</v>
+      </c>
+      <c r="C21" t="str">
+        <v>SPRINKLER-IN</v>
+      </c>
+      <c r="D21" t="str">
+        <v>喷灌</v>
+      </c>
+      <c r="E21" t="str">
+        <v>喷灌主管→上空喷头</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="H21" t="str">
+        <v>P5按最不利喷头入口实测</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>C18</v>
+      </c>
+      <c r="B22" t="str">
+        <v>BUCKET-FILTER-OUT</v>
+      </c>
+      <c r="C22" t="str">
+        <v>ADJ-IN</v>
+      </c>
+      <c r="D22" t="str">
+        <v>肥料吸液</v>
+      </c>
+      <c r="E22" t="str">
+        <v>肥料桶→文丘里</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="H22"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>C19</v>
+      </c>
+      <c r="B23" t="str">
+        <v>ADJ-OUT</v>
+      </c>
+      <c r="C23" t="str">
+        <v>CV-S-IN</v>
+      </c>
+      <c r="D23" t="str">
+        <v>肥料吸液</v>
+      </c>
+      <c r="E23" t="str">
+        <v>肥料桶→文丘里</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="H23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>C20</v>
+      </c>
+      <c r="B24" t="str">
+        <v>CV-S-OUT</v>
+      </c>
+      <c r="C24" t="str">
+        <v>MV-SOURCE-F</v>
+      </c>
+      <c r="D24" t="str">
+        <v>肥料吸液</v>
+      </c>
+      <c r="E24" t="str">
+        <v>肥料桶→文丘里</v>
+      </c>
+      <c r="F24"/>
+      <c r="G24" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="H24" t="str">
+        <v>MV-SOURCE处于肥料位</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>C21</v>
+      </c>
+      <c r="B25" t="str">
+        <v>PEST-FILTER-OUT</v>
+      </c>
+      <c r="C25" t="str">
+        <v>ADJ-P-IN</v>
+      </c>
+      <c r="D25" t="str">
+        <v>农药吸液</v>
+      </c>
+      <c r="E25" t="str">
+        <v>农药桶→文丘里</v>
+      </c>
+      <c r="F25"/>
+      <c r="G25" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="H25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>C22</v>
+      </c>
+      <c r="B26" t="str">
+        <v>ADJ-P-OUT</v>
+      </c>
+      <c r="C26" t="str">
+        <v>CV-P-IN</v>
+      </c>
+      <c r="D26" t="str">
+        <v>农药吸液</v>
+      </c>
+      <c r="E26" t="str">
+        <v>农药桶→文丘里</v>
+      </c>
+      <c r="F26"/>
+      <c r="G26" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="H26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>C23</v>
+      </c>
+      <c r="B27" t="str">
+        <v>CV-P-OUT</v>
+      </c>
+      <c r="C27" t="str">
+        <v>MV-SOURCE-P</v>
+      </c>
+      <c r="D27" t="str">
+        <v>农药吸液</v>
+      </c>
+      <c r="E27" t="str">
+        <v>农药桶→文丘里</v>
+      </c>
+      <c r="F27"/>
+      <c r="G27" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="H27" t="str">
+        <v>MV-SOURCE处于农药位</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>C24</v>
+      </c>
+      <c r="B28" t="str">
+        <v>MV-SOURCE-COM</v>
+      </c>
+      <c r="C28" t="str">
+        <v>VENTURI-SUCTION</v>
+      </c>
+      <c r="D28" t="str">
+        <v>共用吸液</v>
+      </c>
+      <c r="E28" t="str">
+        <v>吸液汇流→文丘里</v>
+      </c>
+      <c r="F28"/>
+      <c r="G28" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="H28" t="str">
+        <v>一只三通选择阀在肥料/关闭/农药之间单选</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+    </row>
+    <row r="30">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+    </row>
+    <row r="31">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+    </row>
+    <row r="32">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -2749,7 +3973,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="str">
-        <v>P0–P3动态压力测点</v>
+        <v>P0–P5动态压力测点</v>
       </c>
       <c r="B1" s="4" t="str">
         <v>P0–P3动态压力测点</v>
@@ -2787,7 +4011,7 @@
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="8" t="str">
-        <v>测压口G1/4（2分）为候选；实际可采用带测压口三通或临时测压接头，端口形式与密封必须按实物确认。</v>
+        <v>P1/P2须分别记录滴灌施肥与喷灌喷药工况；P4验证滴头压力，P5按最不利上空喷头入口位置实测。</v>
       </c>
       <c r="B2" s="8" t="str">
         <v>测压口G1/4（2分）为候选；实际可采用带测压口三通或临时测压接头，端口形式与密封必须按实物确认。</v>
@@ -2872,7 +4096,7 @@
         <v>共用上游动态压力</v>
       </c>
       <c r="D5" s="20" t="str">
-        <v>A路/B路</v>
+        <v>A路/B路、滴灌/喷灌</v>
       </c>
       <c r="E5" s="22" t="str">
         <v>G</v>
@@ -2908,7 +4132,7 @@
         <v>文丘里入口动态压力</v>
       </c>
       <c r="D6" s="21" t="str">
-        <v>仅B路</v>
+        <v>B路；两种末端分别记录</v>
       </c>
       <c r="E6" s="23" t="str">
         <v>G</v>
@@ -2944,7 +4168,7 @@
         <v>文丘里出口动态压力</v>
       </c>
       <c r="D7" s="21" t="str">
-        <v>仅B路</v>
+        <v>B路；两种末端分别记录</v>
       </c>
       <c r="E7" s="23" t="str">
         <v>G</v>
@@ -2974,13 +4198,13 @@
         <v>P3</v>
       </c>
       <c r="B8" s="21" t="str">
-        <v>减压阀后、主管前</v>
+        <v>A/B合流后、MV-END入口前</v>
       </c>
       <c r="C8" s="21" t="str">
-        <v>滴灌主管供水压力</v>
+        <v>共用下游动态压力</v>
       </c>
       <c r="D8" s="21" t="str">
-        <v>A路/B路</v>
+        <v>A路/B路、滴灌/喷灌</v>
       </c>
       <c r="E8" s="23" t="str">
         <v>G</v>
@@ -3002,7 +4226,79 @@
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="23" t="str">
+        <v>验证公共段及末端三通选择阀入口压力</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>P4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>滴灌减压阀后、滴灌主管前</v>
+      </c>
+      <c r="C9" t="str">
+        <v>滴灌主管供水压力</v>
+      </c>
+      <c r="D9" t="str">
+        <v>清水滴灌/滴灌施肥</v>
+      </c>
+      <c r="E9" t="str">
+        <v>G</v>
+      </c>
+      <c r="F9" t="str">
+        <v>1/4</v>
+      </c>
+      <c r="G9" t="str">
+        <v>俗称2分</v>
+      </c>
+      <c r="H9" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="I9" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="J9" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9" t="str">
         <v>验证滴头压力</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>P5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>最不利上空喷头入口</v>
+      </c>
+      <c r="C10" t="str">
+        <v>喷灌末端工作压力</v>
+      </c>
+      <c r="D10" t="str">
+        <v>清水喷灌/上空喷药</v>
+      </c>
+      <c r="E10" t="str">
+        <v>G</v>
+      </c>
+      <c r="F10" t="str">
+        <v>1/4</v>
+      </c>
+      <c r="G10" t="str">
+        <v>俗称2分</v>
+      </c>
+      <c r="H10" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="I10" t="str">
+        <v>待确认</v>
+      </c>
+      <c r="J10" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="K10"/>
+      <c r="L10" t="str">
+        <v>验证喷头压力与覆盖条件</v>
       </c>
     </row>
   </sheetData>
@@ -3039,7 +4335,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="str">
-        <v>主管、支管与吸肥软管</v>
+        <v>滴灌、喷灌与双吸液管材</v>
       </c>
       <c r="B1" s="4" t="str">
         <v>主管、支管与吸肥软管</v>
@@ -3107,6 +4403,19 @@
         <v>管材以毫米内径/外径记录，不使用“几分牙”。实际内径用于水力计算，外径用于接头和卡箍匹配。</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="14" t="str">
         <v>管材ID</v>
@@ -3147,10 +4456,10 @@
         <v>PIPE-MAIN</v>
       </c>
       <c r="B5" s="20" t="str">
-        <v>9/12 PE主管</v>
+        <v>9/12滴灌主管</v>
       </c>
       <c r="C5" s="20" t="str">
-        <v>合流减压后主管</v>
+        <v>滴灌减压阀后至滴灌支管</v>
       </c>
       <c r="D5" s="22" t="str">
         <v>PE</v>
@@ -3178,10 +4487,10 @@
         <v>PIPE-LATERAL</v>
       </c>
       <c r="B6" s="21" t="str">
-        <v>3/5支管</v>
+        <v>3/5滴灌支管</v>
       </c>
       <c r="C6" s="21" t="str">
-        <v>主管至滴头</v>
+        <v>滴灌主管至压力补偿滴头</v>
       </c>
       <c r="D6" s="23" t="str">
         <v>PE/PVC待确认</v>
@@ -3206,21 +4515,21 @@
     </row>
     <row r="7">
       <c r="A7" s="21" t="str">
-        <v>PIPE-SUCTION</v>
+        <v>PIPE-SPRAY</v>
       </c>
       <c r="B7" s="21" t="str">
-        <v>吸肥软管</v>
+        <v>喷灌主管/立管</v>
       </c>
       <c r="C7" s="21" t="str">
-        <v>肥液桶至文丘里侧吸口</v>
+        <v>喷灌调压阀至上空喷头</v>
       </c>
       <c r="D7" s="23" t="str">
-        <v>耐肥软管待确认</v>
+        <v>PE/耐农药材料待确认</v>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="23"/>
       <c r="G7" s="23" t="str">
-        <v>软管倒钩/卡箍</v>
+        <v>PE管接头/卡箍</v>
       </c>
       <c r="H7" s="23"/>
       <c r="I7" s="23" t="str">
@@ -3228,7 +4537,63 @@
       </c>
       <c r="J7" s="23"/>
       <c r="K7" s="23" t="str">
-        <v>必须与文丘里侧吸口和CV-S匹配</v>
+        <v>不得直接套用9/12；按喷头总流量重新计算</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PIPE-SUCTION-F</v>
+      </c>
+      <c r="B8" t="str">
+        <v>肥料吸液软管</v>
+      </c>
+      <c r="C8" t="str">
+        <v>肥料桶至液源三通选择阀</v>
+      </c>
+      <c r="D8" t="str">
+        <v>耐肥软管待确认</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8" t="str">
+        <v>软管倒钩/卡箍</v>
+      </c>
+      <c r="H8"/>
+      <c r="I8" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8" t="str">
+        <v>与CV-F、MV-SOURCE及文丘里吸口匹配</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>PIPE-SUCTION-P</v>
+      </c>
+      <c r="B9" t="str">
+        <v>农药吸液软管</v>
+      </c>
+      <c r="C9" t="str">
+        <v>农药桶至液源三通选择阀</v>
+      </c>
+      <c r="D9" t="str">
+        <v>耐具体农药制剂软管待确认</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9" t="str">
+        <v>软管倒钩/卡箍</v>
+      </c>
+      <c r="H9"/>
+      <c r="I9" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="J9" t="str">
+        <v>https://zzys.moa.gov.cn/zcjd/201705/t20170506_5597923.htm</v>
+      </c>
+      <c r="K9" t="str">
+        <v>与CV-P、MV-SOURCE及文丘里吸口匹配</v>
       </c>
     </row>
   </sheetData>
@@ -3379,7 +4744,27 @@
         <v>https://std.samr.gov.cn/gb/search/gbDetailed?id=71F772D81C67D3A7E05397BE0A0AB82A</v>
       </c>
       <c r="J5" s="22" t="str">
-        <v>目数不自动换算为固定微米；压损须取同一型号工况</v>
+        <v>公共水源过滤；目数不自动换算为固定微米</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FILTER-S</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6" t="str">
+        <v>喷灌支路过滤器待确认</v>
+      </c>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6" t="str">
+        <v>待厂家确认</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6" t="str">
+        <v>过滤精度按拟购喷头及农药制剂要求</v>
       </c>
     </row>
   </sheetData>
